--- a/engine/sc/qa/unit/data/xlsx/pivot-table/PivotTableCellFormatsTest_15_TwoDataFieldColumns_WholeDataColumnSelected.xlsx
+++ b/engine/sc/qa/unit/data/xlsx/pivot-table/PivotTableCellFormatsTest_15_TwoDataFieldColumns_WholeDataColumnSelected.xlsx
@@ -1,39 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\VBOXSVR\quikee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03797ADD-2E36-4B06-AEC2-74A2A2712812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{03797ADD-2E36-4B06-AEC2-74A2A2712812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5734F67-7A92-4502-A0F5-653AD3531C1F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="16224" xr2:uid="{D77C3CC8-6808-493C-9198-7EE457FDC5AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId2"/>
+    <pivotCache cacheId="119" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="12">
   <si>
     <t>A</t>
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of B</t>
+  </si>
+  <si>
+    <t>Sum of C</t>
   </si>
   <si>
     <t>a</t>
@@ -53,24 +76,12 @@
   <si>
     <t>f</t>
   </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Sum of B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Sum of C</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -101,17 +112,100 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -135,72 +229,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A695139-ABF8-99C1-C190-7A1C3F4B0405}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3048000" y="1645920"/>
-          <a:ext cx="2042160" cy="1287780"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -390,7 +418,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3587548F-E7E5-4F83-ADC1-D1BCD090259C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3587548F-E7E5-4F83-ADC1-D1BCD090259C}" name="PivotTable1" cacheId="119" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="F1:H7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
@@ -455,7 +483,7 @@
       </pivotArea>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight15" showRowHeaders="0" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo showRowHeaders="0" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -765,13 +793,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E559A02-FAA2-4FD3-AB40-361DCD664D06}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -779,21 +807,21 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -801,19 +829,19 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="5">
         <v>5</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="10">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -821,19 +849,19 @@
       <c r="C3">
         <v>9</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3">
+      <c r="F3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="7">
+        <v>10</v>
+      </c>
+      <c r="H3" s="11">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -841,19 +869,19 @@
       <c r="C4">
         <v>7</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="7">
         <v>15</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="11">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -861,19 +889,19 @@
       <c r="C5">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="F5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="7">
+        <v>10</v>
+      </c>
+      <c r="H5" s="11">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -881,50 +909,50 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="7">
+        <v>15</v>
+      </c>
+      <c r="H6" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="9">
+        <v>5</v>
+      </c>
+      <c r="H7" s="12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15">
+      <c r="A9" t="s">
         <v>7</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -932,10 +960,19 @@
       <c r="C9">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -943,10 +980,19 @@
       <c r="C10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="5">
+        <v>5</v>
+      </c>
+      <c r="H10" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -954,10 +1000,19 @@
       <c r="C11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="7">
+        <v>10</v>
+      </c>
+      <c r="H11" s="11">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -965,32 +1020,59 @@
       <c r="C12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="7">
+        <v>15</v>
+      </c>
+      <c r="H12" s="11">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="7">
+        <v>10</v>
+      </c>
+      <c r="H13" s="11">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7">
+        <v>15</v>
+      </c>
+      <c r="H14" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
         <v>7</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>3</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -998,10 +1080,19 @@
       <c r="C15">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="9">
+        <v>5</v>
+      </c>
+      <c r="H15" s="12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -1010,9 +1101,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -1021,9 +1112,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -1032,31 +1123,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>7</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>3</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -1065,9 +1156,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -1076,9 +1167,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -1087,9 +1178,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -1098,9 +1189,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1109,9 +1200,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1120,9 +1211,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -1131,9 +1222,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -1142,9 +1233,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -1153,9 +1244,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -1164,9 +1255,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1177,6 +1268,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>